--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.68316</v>
+        <v>16.80694</v>
       </c>
       <c r="D2" t="n">
         <v>16.41022</v>
       </c>
       <c r="E2" t="n">
-        <v>16.80694</v>
+        <v>16.68316</v>
       </c>
       <c r="F2" t="n">
         <v>42.85079</v>
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.44035</v>
+        <v>16.82717</v>
       </c>
       <c r="D3" t="n">
         <v>16.24561</v>
       </c>
       <c r="E3" t="n">
-        <v>16.82717</v>
+        <v>16.44035</v>
       </c>
       <c r="F3" t="n">
         <v>42.92889</v>
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.69136</v>
+        <v>16.78328</v>
       </c>
       <c r="D8" t="n">
         <v>15.54579</v>
       </c>
       <c r="E8" t="n">
-        <v>16.78328</v>
+        <v>16.69136</v>
       </c>
       <c r="F8" t="n">
         <v>21.53224</v>
